--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487739_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487739_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.7521</v>
+        <v>9.589600000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6887</v>
+        <v>6.6897</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0634</v>
+        <v>2.8999</v>
       </c>
       <c r="G2" t="n">
         <v>6.7618</v>
@@ -610,13 +610,13 @@
         <v>2.3284</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8739</v>
+        <v>-0.0364</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5204</v>
+        <v>0.4806</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3535</v>
+        <v>-0.517</v>
       </c>
       <c r="V2" t="n">
         <v>1.506</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7015</v>
+        <v>5.1432</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5578</v>
+        <v>2.9177</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1437</v>
+        <v>2.2255</v>
       </c>
       <c r="G3" t="n">
         <v>2.6588</v>
@@ -688,13 +688,13 @@
         <v>2.7164</v>
       </c>
       <c r="S3" t="n">
-        <v>1.268</v>
+        <v>0.7097</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0278</v>
+        <v>1.3876</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7597</v>
+        <v>-0.678</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9418</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1508</v>
+        <v>2.9876</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1308</v>
+        <v>0.6515</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2816</v>
+        <v>2.3361</v>
       </c>
       <c r="G4" t="n">
         <v>2.2167</v>
@@ -766,13 +766,13 @@
         <v>1.5523</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9585</v>
+        <v>-0.1217</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0595</v>
+        <v>0.7228</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.899</v>
+        <v>-0.8445</v>
       </c>
       <c r="V4" t="n">
         <v>-0.6597</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4672</v>
+        <v>1.9098</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0743</v>
+        <v>0.2865</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5415</v>
+        <v>1.6233</v>
       </c>
       <c r="G5" t="n">
         <v>2.7586</v>
@@ -844,13 +844,13 @@
         <v>1.1642</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3212</v>
+        <v>0.1214</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.1719</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2115</v>
+        <v>0.2933</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0611</v>
+        <v>1.3585</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8036</v>
+        <v>2.2646</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7426</v>
+        <v>-0.9061</v>
       </c>
       <c r="G6" t="n">
         <v>1.0868</v>
@@ -922,13 +922,13 @@
         <v>1.5523</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3026</v>
+        <v>0.6</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3039</v>
+        <v>0.7649</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0013</v>
+        <v>-0.1649</v>
       </c>
       <c r="V6" t="n">
         <v>1.2239</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1306</v>
+        <v>0.5976</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.1802</v>
+        <v>-2.6587</v>
       </c>
       <c r="F7" t="n">
-        <v>3.3108</v>
+        <v>3.2563</v>
       </c>
       <c r="G7" t="n">
         <v>0.2039</v>
@@ -1000,13 +1000,13 @@
         <v>0.7761</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1207</v>
+        <v>0.5877</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3163</v>
+        <v>0.8378</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1956</v>
+        <v>-0.2501</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0481</v>
+        <v>0.2855</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.9399</v>
+        <v>-2.579</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8918</v>
+        <v>2.8645</v>
       </c>
       <c r="G8" t="n">
         <v>0.4835</v>
@@ -1078,13 +1078,13 @@
         <v>3.1045</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0182</v>
+        <v>0.3154</v>
       </c>
       <c r="T8" t="n">
-        <v>0.572</v>
+        <v>0.9328</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5901</v>
+        <v>-0.6173999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>-0.7075</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7304</v>
+        <v>-0.3758</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1168</v>
+        <v>-0.7349</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3864</v>
+        <v>0.3591</v>
       </c>
       <c r="G9" t="n">
         <v>1.3749</v>
@@ -1156,13 +1156,13 @@
         <v>1.1642</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3457</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0595</v>
+        <v>0.3224</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2862</v>
+        <v>-0.3135</v>
       </c>
       <c r="V9" t="n">
         <v>-2.7298</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ CAÑAS</t>
+          <t>A. GOMEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7569</v>
+        <v>-1.1346</v>
       </c>
       <c r="E10" t="n">
-        <v>0.356</v>
+        <v>-1.8263</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1128</v>
+        <v>0.6917</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5092</v>
+        <v>-1.3614</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0504</v>
+        <v>-0.3287</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4588</v>
+        <v>-1.0327</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1546</v>
+        <v>-1.6112</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9516</v>
+        <v>-0.3172</v>
       </c>
       <c r="L10" t="n">
-        <v>0.203</v>
+        <v>-1.2941</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3546</v>
+        <v>0.2498</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0989</v>
+        <v>-0.0115</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2558</v>
+        <v>0.2614</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.7463</v>
+        <v>0.194</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1045</v>
+        <v>-0.194</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3582</v>
+        <v>0.3881</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2683</v>
+        <v>0.0328</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3059</v>
+        <v>-0.021</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0377</v>
+        <v>0.0538</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.788</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. GOMEZ GONZALEZ</t>
+          <t>D. FERNANDEZ CAÑAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9621</v>
+        <v>-1.5521</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9264</v>
+        <v>-0.6845</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9643</v>
+        <v>-0.8675</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3614</v>
+        <v>1.5092</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3287</v>
+        <v>1.0504</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0327</v>
+        <v>0.4588</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.6112</v>
+        <v>1.1546</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3172</v>
+        <v>0.9516</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2941</v>
+        <v>0.203</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2498</v>
+        <v>0.3546</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0115</v>
+        <v>0.0989</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2614</v>
+        <v>0.2558</v>
       </c>
       <c r="P11" t="n">
-        <v>0.194</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.194</v>
+        <v>-3.1045</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2053</v>
+        <v>0.473</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1211</v>
+        <v>1.2654</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3264</v>
+        <v>-0.7924</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.788</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2875</v>
+        <v>-2.4226</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2544</v>
+        <v>-5.6348</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9669</v>
+        <v>3.2122</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4522</v>
@@ -1390,13 +1390,13 @@
         <v>2.3284</v>
       </c>
       <c r="S12" t="n">
-        <v>1.9603</v>
+        <v>0.8252</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5134</v>
+        <v>1.133</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5531</v>
+        <v>-0.3078</v>
       </c>
       <c r="V12" t="n">
         <v>-2.2134</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>15.4783</v>
+        <v>16.3867</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.216700000000001</v>
+        <v>-1.308199999999999</v>
       </c>
       <c r="F13" t="n">
         <v>17.695</v>
@@ -1444,7 +1444,7 @@
         <v>3.628700000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.625900000000001</v>
+        <v>-0.6259000000000006</v>
       </c>
       <c r="L13" t="n">
         <v>4.2547</v>
@@ -1468,13 +1468,13 @@
         <v>18.4331</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6077</v>
+        <v>3.5161</v>
       </c>
       <c r="T13" t="n">
-        <v>6.746</v>
+        <v>7.6544</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.1383</v>
+        <v>-4.138500000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-6.3103</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. NIMAGA</t>
+          <t>B. FERNANDEZ SHEPHARD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.741</v>
+        <v>2.8468</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6543</v>
+        <v>1.5866</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0867</v>
+        <v>1.2602</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4109</v>
+        <v>-0.539</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1623</v>
+        <v>1.3462</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2486</v>
+        <v>-1.8852</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2931</v>
+        <v>-0.3542</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3336</v>
+        <v>1.6477</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0406</v>
+        <v>-2.002</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1179</v>
+        <v>-0.1848</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1714</v>
+        <v>-0.3015</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2892</v>
+        <v>0.1168</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3582</v>
+        <v>0.9702</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3582</v>
+        <v>0.9702</v>
       </c>
       <c r="S14" t="n">
-        <v>3.0758</v>
+        <v>0.4366</v>
       </c>
       <c r="T14" t="n">
-        <v>3.6652</v>
+        <v>0.4349</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5895</v>
+        <v>0.0017</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2821</v>
+        <v>1.9791</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2821</v>
+        <v>1.506</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5642</v>
+        <v>0.4732</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. FERNANDEZ SHEPHARD</t>
+          <t>M. NIMAGA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3313</v>
+        <v>1.7574</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2863</v>
+        <v>1.7524</v>
       </c>
       <c r="F15" t="n">
-        <v>1.045</v>
+        <v>0.005</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.539</v>
+        <v>-0.4109</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3462</v>
+        <v>-0.1623</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.8852</v>
+        <v>-0.2486</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3542</v>
+        <v>-0.2931</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6477</v>
+        <v>-0.3336</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.002</v>
+        <v>0.0406</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1848</v>
+        <v>-0.1179</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3015</v>
+        <v>0.1714</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1168</v>
+        <v>-0.2892</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9702</v>
+        <v>1.3582</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9702</v>
+        <v>1.3582</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.079</v>
+        <v>1.0921</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1346</v>
+        <v>1.7634</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2135</v>
+        <v>-0.6712</v>
       </c>
       <c r="V15" t="n">
-        <v>1.9791</v>
+        <v>-0.2821</v>
       </c>
       <c r="W15" t="n">
-        <v>1.506</v>
+        <v>0.2821</v>
       </c>
       <c r="X15" t="n">
-        <v>0.4732</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8361</v>
+        <v>0.8117</v>
       </c>
       <c r="E16" t="n">
-        <v>0.77</v>
+        <v>0.3696</v>
       </c>
       <c r="F16" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.4421</v>
       </c>
       <c r="G16" t="n">
         <v>-0.4472</v>
@@ -1702,13 +1702,13 @@
         <v>1.5523</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7763</v>
+        <v>-0.8008</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0258</v>
+        <v>-0.3746</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8021</v>
+        <v>-0.4262</v>
       </c>
       <c r="V16" t="n">
         <v>2.4477</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.183</v>
+        <v>0.0139</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7525</v>
+        <v>1.6524</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9355</v>
+        <v>-1.6385</v>
       </c>
       <c r="G17" t="n">
         <v>-2.6333</v>
@@ -1780,13 +1780,13 @@
         <v>1.3582</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5572</v>
+        <v>-0.3603</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8748</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.432</v>
+        <v>-1.135</v>
       </c>
       <c r="V17" t="n">
         <v>1.6493</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3576</v>
+        <v>-0.2486</v>
       </c>
       <c r="E18" t="n">
         <v>-0.371</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0134</v>
+        <v>0.1224</v>
       </c>
       <c r="G18" t="n">
         <v>-0.3215</v>
@@ -1858,13 +1858,13 @@
         <v>0.7761</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8122</v>
+        <v>-0.7032</v>
       </c>
       <c r="T18" t="n">
         <v>-0.4116</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4006</v>
+        <v>-0.2916</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4588</v>
+        <v>-0.7886</v>
       </c>
       <c r="E19" t="n">
         <v>-3.1646</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7059</v>
+        <v>2.376</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6447000000000001</v>
@@ -1936,13 +1936,13 @@
         <v>2.1344</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7084</v>
+        <v>0.3785</v>
       </c>
       <c r="T19" t="n">
         <v>0.2075</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5009</v>
+        <v>0.1711</v>
       </c>
       <c r="V19" t="n">
         <v>1.2239</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1002</v>
+        <v>-2.3327</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.2312</v>
+        <v>-3.7307</v>
       </c>
       <c r="F20" t="n">
-        <v>1.131</v>
+        <v>1.398</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1101</v>
@@ -2014,13 +2014,13 @@
         <v>2.5224</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.196</v>
+        <v>-1.4286</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9567</v>
+        <v>-0.4562</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.2393</v>
+        <v>-0.9724</v>
       </c>
       <c r="V20" t="n">
         <v>0.5642</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.311</v>
+        <v>-4.4957</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.2326</v>
+        <v>-6.3327</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9216</v>
+        <v>1.837</v>
       </c>
       <c r="G21" t="n">
         <v>-2.9645</v>
@@ -2092,13 +2092,13 @@
         <v>2.5224</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9818</v>
+        <v>0.7972</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8871</v>
+        <v>0.787</v>
       </c>
       <c r="U21" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.0101</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.335</v>
+        <v>-4.5376</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.1374</v>
+        <v>-4.6369</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1976</v>
+        <v>0.0994</v>
       </c>
       <c r="G22" t="n">
         <v>-3.8687</v>
@@ -2170,13 +2170,13 @@
         <v>1.3582</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8365</v>
+        <v>-0.039</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4015</v>
+        <v>0.902</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.238</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-0.0478</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.641</v>
+        <v>-7.1701</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.021</v>
+        <v>-4.8199</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.62</v>
+        <v>-2.3502</v>
       </c>
       <c r="G23" t="n">
         <v>-5.3007</v>
@@ -2248,13 +2248,13 @@
         <v>1.9403</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.1164</v>
+        <v>-0.6455</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6898</v>
+        <v>0.5114</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.4266</v>
+        <v>-1.1569</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2239</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-15.4782</v>
+        <v>-14.1435</v>
       </c>
       <c r="E24" t="n">
-        <v>-17.6947</v>
+        <v>-17.6948</v>
       </c>
       <c r="F24" t="n">
-        <v>2.2167</v>
+        <v>3.551399999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-17.2406</v>
@@ -2326,13 +2326,13 @@
         <v>16.4927</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.6076</v>
+        <v>-1.273</v>
       </c>
       <c r="T24" t="n">
-        <v>4.138400000000001</v>
+        <v>4.138500000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.746</v>
+        <v>-5.4114</v>
       </c>
       <c r="V24" t="n">
         <v>6.310400000000001</v>
